--- a/data/summarized fitur aset - KBMI 4.xlsx
+++ b/data/summarized fitur aset - KBMI 4.xlsx
@@ -552,10 +552,10 @@
         <v>0.01075527276849911</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01657891300236998</v>
+        <v>0.6543130362564963</v>
       </c>
       <c r="N2" t="n">
-        <v>1.01602820361624</v>
+        <v>0.02574401282309871</v>
       </c>
     </row>
     <row r="3">
@@ -606,10 +606,10 @@
         <v>0.00890923687556004</v>
       </c>
       <c r="M3" t="n">
-        <v>0.02464141077589152</v>
+        <v>0.7020133223751425</v>
       </c>
       <c r="N3" t="n">
-        <v>1.062915473956672</v>
+        <v>0.03730945835216132</v>
       </c>
     </row>
     <row r="4">
@@ -660,10 +660,10 @@
         <v>0.02450315162864658</v>
       </c>
       <c r="M4" t="n">
-        <v>0.02029818009733492</v>
+        <v>0.6699885287604143</v>
       </c>
       <c r="N4" t="n">
-        <v>1.090963168889033</v>
+        <v>0.03305215825506711</v>
       </c>
     </row>
     <row r="5">
@@ -714,10 +714,10 @@
         <v>0.006957662156682413</v>
       </c>
       <c r="M5" t="n">
-        <v>0.02794918680291551</v>
+        <v>0.6400007606409356</v>
       </c>
       <c r="N5" t="n">
-        <v>1.003522863032366</v>
+        <v>0.04382439785196439</v>
       </c>
     </row>
     <row r="6">
@@ -768,10 +768,10 @@
         <v>0.00808939585906817</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02719381003643478</v>
+        <v>0.5773360395628229</v>
       </c>
       <c r="N6" t="n">
-        <v>1.010969675115811</v>
+        <v>0.04761891760388536</v>
       </c>
     </row>
     <row r="7">
@@ -822,10 +822,10 @@
         <v>0.007887406245276771</v>
       </c>
       <c r="M7" t="n">
-        <v>0.04605275499795481</v>
+        <v>0.6230473013911807</v>
       </c>
       <c r="N7" t="n">
-        <v>1.031680658241608</v>
+        <v>0.07625702973761733</v>
       </c>
     </row>
     <row r="8">
@@ -876,10 +876,10 @@
         <v>0.02245901525693728</v>
       </c>
       <c r="M8" t="n">
-        <v>0.04769000277953852</v>
+        <v>0.647270856516703</v>
       </c>
       <c r="N8" t="n">
-        <v>1.037349628860651</v>
+        <v>0.07643045594536366</v>
       </c>
     </row>
     <row r="9">
@@ -930,10 +930,10 @@
         <v>0.005689154035014207</v>
       </c>
       <c r="M9" t="n">
-        <v>0.04196354137965498</v>
+        <v>0.64547614663133</v>
       </c>
       <c r="N9" t="n">
-        <v>1.058670050634366</v>
+        <v>0.06882600497175419</v>
       </c>
     </row>
     <row r="10">
@@ -984,10 +984,10 @@
         <v>0.008097578411057509</v>
       </c>
       <c r="M10" t="n">
-        <v>0.02550723165469695</v>
+        <v>0.544935047026507</v>
       </c>
       <c r="N10" t="n">
-        <v>1.023431396392182</v>
+        <v>0.04790461148151398</v>
       </c>
     </row>
     <row r="11">
@@ -1038,10 +1038,10 @@
         <v>0.008287748053300835</v>
       </c>
       <c r="M11" t="n">
-        <v>0.04837820318119871</v>
+        <v>0.6315754479570467</v>
       </c>
       <c r="N11" t="n">
-        <v>1.033625668956791</v>
+        <v>0.07917494701202332</v>
       </c>
     </row>
     <row r="12">
@@ -1092,10 +1092,10 @@
         <v>0.02651778575642104</v>
       </c>
       <c r="M12" t="n">
-        <v>0.05231951530634381</v>
+        <v>0.674368266412619</v>
       </c>
       <c r="N12" t="n">
-        <v>1.036881400117148</v>
+        <v>0.08044437288379079</v>
       </c>
     </row>
     <row r="13">
@@ -1146,10 +1146,10 @@
         <v>0.004764252658911321</v>
       </c>
       <c r="M13" t="n">
-        <v>0.04510475612294877</v>
+        <v>0.6194223167806974</v>
       </c>
       <c r="N13" t="n">
-        <v>1.036091072678112</v>
+        <v>0.07544551413192954</v>
       </c>
     </row>
     <row r="14">
@@ -1200,10 +1200,10 @@
         <v>0.009826595588117137</v>
       </c>
       <c r="M14" t="n">
-        <v>0.02754209810427008</v>
+        <v>0.5357667436378493</v>
       </c>
       <c r="N14" t="n">
-        <v>1.035906784083837</v>
+        <v>0.05325273845926031</v>
       </c>
     </row>
     <row r="15">
@@ -1254,10 +1254,10 @@
         <v>0.007995493336151174</v>
       </c>
       <c r="M15" t="n">
-        <v>0.04788172130255296</v>
+        <v>0.6214711828178504</v>
       </c>
       <c r="N15" t="n">
-        <v>1.026814076317421</v>
+        <v>0.07911167370439323</v>
       </c>
     </row>
     <row r="16">
@@ -1308,10 +1308,10 @@
         <v>0.02484901372153656</v>
       </c>
       <c r="M16" t="n">
-        <v>0.05488417536485788</v>
+        <v>0.6641789343593151</v>
       </c>
       <c r="N16" t="n">
-        <v>1.027789865675865</v>
+        <v>0.08493102732984435</v>
       </c>
     </row>
     <row r="17">
@@ -1362,10 +1362,10 @@
         <v>0.003918431706350286</v>
       </c>
       <c r="M17" t="n">
-        <v>0.05188224801669713</v>
+        <v>0.6523125705398802</v>
       </c>
       <c r="N17" t="n">
-        <v>1.027678657225814</v>
+        <v>0.08173731640880014</v>
       </c>
     </row>
     <row r="18">
@@ -1416,10 +1416,10 @@
         <v>0.009995710124041378</v>
       </c>
       <c r="M18" t="n">
-        <v>0.02877990352133709</v>
+        <v>0.5226731350776493</v>
       </c>
       <c r="N18" t="n">
-        <v>1.022842504629262</v>
+        <v>0.05632068423868711</v>
       </c>
     </row>
     <row r="19">
@@ -1470,10 +1470,10 @@
         <v>0.006792190309852888</v>
       </c>
       <c r="M19" t="n">
-        <v>0.04868571576224905</v>
+        <v>0.6509184930744206</v>
       </c>
       <c r="N19" t="n">
-        <v>1.026380902133355</v>
+        <v>0.07676858070055186</v>
       </c>
     </row>
     <row r="20">
@@ -1524,10 +1524,10 @@
         <v>0.02424449042911652</v>
       </c>
       <c r="M20" t="n">
-        <v>0.05661926532116838</v>
+        <v>0.666907467483271</v>
       </c>
       <c r="N20" t="n">
-        <v>1.029778324082162</v>
+        <v>0.0874263597215735</v>
       </c>
     </row>
     <row r="21">
@@ -1578,10 +1578,10 @@
         <v>0.004013426982055066</v>
       </c>
       <c r="M21" t="n">
-        <v>0.05458174171201331</v>
+        <v>0.6461226034051759</v>
       </c>
       <c r="N21" t="n">
-        <v>1.031571564638912</v>
+        <v>0.08714286174456946</v>
       </c>
     </row>
     <row r="22">
@@ -1632,10 +1632,10 @@
         <v>0.01092964117340185</v>
       </c>
       <c r="M22" t="n">
-        <v>0.0279850854585897</v>
+        <v>0.5147438455478128</v>
       </c>
       <c r="N22" t="n">
-        <v>1.02066364081003</v>
+        <v>0.05549043365860082</v>
       </c>
     </row>
     <row r="23">
@@ -1686,10 +1686,10 @@
         <v>0.006378200131800918</v>
       </c>
       <c r="M23" t="n">
-        <v>0.04740124255771754</v>
+        <v>0.6302898941181441</v>
       </c>
       <c r="N23" t="n">
-        <v>1.025242039915222</v>
+        <v>0.07710380107297292</v>
       </c>
     </row>
     <row r="24">
@@ -1740,10 +1740,10 @@
         <v>0.02397144620800645</v>
       </c>
       <c r="M24" t="n">
-        <v>0.05503027287942899</v>
+        <v>0.6364648560376018</v>
       </c>
       <c r="N24" t="n">
-        <v>1.040442772591639</v>
+        <v>0.08995916922672152</v>
       </c>
     </row>
     <row r="25">
@@ -1794,10 +1794,10 @@
         <v>0.003770883875911295</v>
       </c>
       <c r="M25" t="n">
-        <v>0.05171079951746201</v>
+        <v>0.6051617678611098</v>
       </c>
       <c r="N25" t="n">
-        <v>1.023041561308376</v>
+        <v>0.08741843897678331</v>
       </c>
     </row>
     <row r="26">
@@ -1848,10 +1848,10 @@
         <v>0.009506754014840047</v>
       </c>
       <c r="M26" t="n">
-        <v>0.0267024554017725</v>
+        <v>0.5148439288552971</v>
       </c>
       <c r="N26" t="n">
-        <v>1.025678642515216</v>
+        <v>0.05319697227314662</v>
       </c>
     </row>
     <row r="27">
@@ -1902,10 +1902,10 @@
         <v>0.007548074914001441</v>
       </c>
       <c r="M27" t="n">
-        <v>0.04462248711454708</v>
+        <v>0.6109036624659336</v>
       </c>
       <c r="N27" t="n">
-        <v>1.028851647760216</v>
+        <v>0.07515083345489169</v>
       </c>
     </row>
     <row r="28">
@@ -1956,10 +1956,10 @@
         <v>0.02290393659689072</v>
       </c>
       <c r="M28" t="n">
-        <v>0.05334943511207615</v>
+        <v>0.6178181193369826</v>
       </c>
       <c r="N28" t="n">
-        <v>1.033240421291009</v>
+        <v>0.08922171604483611</v>
       </c>
     </row>
     <row r="29">
@@ -2010,10 +2010,10 @@
         <v>0.006015966055517137</v>
       </c>
       <c r="M29" t="n">
-        <v>0.05144533161708193</v>
+        <v>0.6000292937064021</v>
       </c>
       <c r="N29" t="n">
-        <v>1.024187315051129</v>
+        <v>0.08781180621257377</v>
       </c>
     </row>
     <row r="30">
@@ -2064,10 +2064,10 @@
         <v>0.01119446144101002</v>
       </c>
       <c r="M30" t="n">
-        <v>0.02830527814822404</v>
+        <v>0.5022021513820725</v>
       </c>
       <c r="N30" t="n">
-        <v>1.01499278114327</v>
+        <v>0.05720734749868165</v>
       </c>
     </row>
     <row r="31">
@@ -2118,10 +2118,10 @@
         <v>0.007940750188881679</v>
       </c>
       <c r="M31" t="n">
-        <v>0.04513223240318735</v>
+        <v>0.6226510431513592</v>
       </c>
       <c r="N31" t="n">
-        <v>1.027406047455745</v>
+        <v>0.07447049035930227</v>
       </c>
     </row>
     <row r="32">
@@ -2172,10 +2172,10 @@
         <v>0.02391611789032971</v>
       </c>
       <c r="M32" t="n">
-        <v>0.05632285933962994</v>
+        <v>0.6503826320204547</v>
       </c>
       <c r="N32" t="n">
-        <v>1.038904108989339</v>
+        <v>0.08996865401554859</v>
       </c>
     </row>
     <row r="33">
@@ -2226,10 +2226,10 @@
         <v>0.005552587155284447</v>
       </c>
       <c r="M33" t="n">
-        <v>0.05498882336282065</v>
+        <v>0.6326363863308309</v>
       </c>
       <c r="N33" t="n">
-        <v>1.024873201144919</v>
+        <v>0.08908208987773174</v>
       </c>
     </row>
     <row r="34">
@@ -2280,10 +2280,10 @@
         <v>0.01179289987700865</v>
       </c>
       <c r="M34" t="n">
-        <v>0.02886096791604882</v>
+        <v>0.5307188364495358</v>
       </c>
       <c r="N34" t="n">
-        <v>1.016772674802146</v>
+        <v>0.0552930130418881</v>
       </c>
     </row>
     <row r="35">
@@ -2334,10 +2334,10 @@
         <v>0.009183777834109997</v>
       </c>
       <c r="M35" t="n">
-        <v>0.04291998663929377</v>
+        <v>0.6395328479974554</v>
       </c>
       <c r="N35" t="n">
-        <v>1.02901514775923</v>
+        <v>0.06905871454726716</v>
       </c>
     </row>
     <row r="36">
@@ -2388,10 +2388,10 @@
         <v>0.02516709661982215</v>
       </c>
       <c r="M36" t="n">
-        <v>0.05614837741546663</v>
+        <v>0.6755343506418707</v>
       </c>
       <c r="N36" t="n">
-        <v>1.037791236013939</v>
+        <v>0.08625807694724584</v>
       </c>
     </row>
     <row r="37">
@@ -2442,10 +2442,10 @@
         <v>0.005218418746152272</v>
       </c>
       <c r="M37" t="n">
-        <v>0.05731101131233773</v>
+        <v>0.6505184530864599</v>
       </c>
       <c r="N37" t="n">
-        <v>1.021444066634962</v>
+        <v>0.08998974922246523</v>
       </c>
     </row>
     <row r="38">
@@ -2496,10 +2496,10 @@
         <v>0.01217253025992921</v>
       </c>
       <c r="M38" t="n">
-        <v>0.02819437348695034</v>
+        <v>0.5261440302474134</v>
       </c>
       <c r="N38" t="n">
-        <v>1.016808194376687</v>
+        <v>0.05448749458084125</v>
       </c>
     </row>
     <row r="39">
@@ -2550,10 +2550,10 @@
         <v>0.005991101878336911</v>
       </c>
       <c r="M39" t="n">
-        <v>0.04125296286539953</v>
+        <v>0.6290993015103593</v>
       </c>
       <c r="N39" t="n">
-        <v>1.029701327673346</v>
+        <v>0.06752229819835787</v>
       </c>
     </row>
     <row r="40">
@@ -2604,10 +2604,10 @@
         <v>0.02311670420668254</v>
       </c>
       <c r="M40" t="n">
-        <v>0.05607961913958524</v>
+        <v>0.6805225035579979</v>
       </c>
       <c r="N40" t="n">
-        <v>1.044107614278077</v>
+        <v>0.0860414711391911</v>
       </c>
     </row>
     <row r="41">
@@ -2658,10 +2658,10 @@
         <v>0.00539015919188091</v>
       </c>
       <c r="M41" t="n">
-        <v>0.05532606299121029</v>
+        <v>0.6391316572842384</v>
       </c>
       <c r="N41" t="n">
-        <v>1.02532580207194</v>
+        <v>0.08875673621455007</v>
       </c>
     </row>
     <row r="42">
@@ -2712,10 +2712,10 @@
         <v>0.01208937567948008</v>
       </c>
       <c r="M42" t="n">
-        <v>0.02640916591583858</v>
+        <v>0.5385378362985057</v>
       </c>
       <c r="N42" t="n">
-        <v>1.017351350817073</v>
+        <v>0.0498895320022385</v>
       </c>
     </row>
     <row r="43">
@@ -2766,10 +2766,10 @@
         <v>0.007232788062864638</v>
       </c>
       <c r="M43" t="n">
-        <v>0.0345579245808216</v>
+        <v>0.5939119966883081</v>
       </c>
       <c r="N43" t="n">
-        <v>1.031926229324679</v>
+        <v>0.06004463456677625</v>
       </c>
     </row>
     <row r="44">
@@ -2820,10 +2820,10 @@
         <v>0.02001939544604218</v>
       </c>
       <c r="M44" t="n">
-        <v>0.0503031342533605</v>
+        <v>0.6442035187594678</v>
       </c>
       <c r="N44" t="n">
-        <v>1.030352826559046</v>
+        <v>0.08045590415671325</v>
       </c>
     </row>
     <row r="45">
@@ -2874,10 +2874,10 @@
         <v>0.004052964357590595</v>
       </c>
       <c r="M45" t="n">
-        <v>0.04830329886446205</v>
+        <v>0.5881243186397747</v>
       </c>
       <c r="N45" t="n">
-        <v>1.022082869234672</v>
+        <v>0.08394479318772788</v>
       </c>
     </row>
     <row r="46">
@@ -2928,10 +2928,10 @@
         <v>0.01006533674794197</v>
       </c>
       <c r="M46" t="n">
-        <v>0.02699293560057618</v>
+        <v>0.5382738075577017</v>
       </c>
       <c r="N46" t="n">
-        <v>1.01487772998211</v>
+        <v>0.05089329784067081</v>
       </c>
     </row>
     <row r="47">
@@ -2982,10 +2982,10 @@
         <v>0.00795295246756814</v>
       </c>
       <c r="M47" t="n">
-        <v>0.03574869180797206</v>
+        <v>0.629111779390783</v>
       </c>
       <c r="N47" t="n">
-        <v>1.034494574704442</v>
+        <v>0.05878419215729921</v>
       </c>
     </row>
     <row r="48">
@@ -3036,10 +3036,10 @@
         <v>0.01768928650069429</v>
       </c>
       <c r="M48" t="n">
-        <v>0.05111630492553221</v>
+        <v>0.6432080485751298</v>
       </c>
       <c r="N48" t="n">
-        <v>1.022908704464536</v>
+        <v>0.08129144740060401</v>
       </c>
     </row>
     <row r="49">
@@ -3090,10 +3090,10 @@
         <v>0.004754168156210271</v>
       </c>
       <c r="M49" t="n">
-        <v>0.05083306336915244</v>
+        <v>0.6267809953593146</v>
       </c>
       <c r="N49" t="n">
-        <v>1.023327534666394</v>
+        <v>0.08299369923823946</v>
       </c>
     </row>
     <row r="50">
@@ -3144,10 +3144,10 @@
         <v>0.0100136610160599</v>
       </c>
       <c r="M50" t="n">
-        <v>0.02619691316701024</v>
+        <v>0.5405245177302375</v>
       </c>
       <c r="N50" t="n">
-        <v>1.015644640848093</v>
+        <v>0.04922395486621679</v>
       </c>
     </row>
     <row r="51">
@@ -3198,10 +3198,10 @@
         <v>0.006195471490433611</v>
       </c>
       <c r="M51" t="n">
-        <v>0.03348213887675885</v>
+        <v>0.6443648955627385</v>
       </c>
       <c r="N51" t="n">
-        <v>1.049006243276712</v>
+        <v>0.05450789290640089</v>
       </c>
     </row>
     <row r="52">
@@ -3252,10 +3252,10 @@
         <v>0.01797350990008636</v>
       </c>
       <c r="M52" t="n">
-        <v>0.0493515816878574</v>
+        <v>0.6520427595006858</v>
       </c>
       <c r="N52" t="n">
-        <v>1.020771413079048</v>
+        <v>0.07725978556341484</v>
       </c>
     </row>
     <row r="53">
@@ -3306,10 +3306,10 @@
         <v>0.004521622380496413</v>
       </c>
       <c r="M53" t="n">
-        <v>0.0474485143699144</v>
+        <v>0.646602237457938</v>
       </c>
       <c r="N53" t="n">
-        <v>1.032827671412701</v>
+        <v>0.07579023976368264</v>
       </c>
     </row>
     <row r="54">
@@ -3360,10 +3360,10 @@
         <v>0.009801839037172848</v>
       </c>
       <c r="M54" t="n">
-        <v>0.02557367741508091</v>
+        <v>0.5526281768569941</v>
       </c>
       <c r="N54" t="n">
-        <v>1.014443035613116</v>
+        <v>0.0469448356692436</v>
       </c>
     </row>
     <row r="55">
@@ -3414,10 +3414,10 @@
         <v>0.008166697929512988</v>
       </c>
       <c r="M55" t="n">
-        <v>0.02994685996667913</v>
+        <v>0.6515018816757246</v>
       </c>
       <c r="N55" t="n">
-        <v>1.053583006591842</v>
+        <v>0.04842887434265763</v>
       </c>
     </row>
     <row r="56">
@@ -3468,10 +3468,10 @@
         <v>0.02101080373134009</v>
       </c>
       <c r="M56" t="n">
-        <v>0.05039723977149593</v>
+        <v>0.6845072682917085</v>
       </c>
       <c r="N56" t="n">
-        <v>1.021087512869041</v>
+        <v>0.07517815310006526</v>
       </c>
     </row>
     <row r="57">
@@ -3522,10 +3522,10 @@
         <v>0.005246835801358314</v>
       </c>
       <c r="M57" t="n">
-        <v>0.04623179573185095</v>
+        <v>0.6581686870837286</v>
       </c>
       <c r="N57" t="n">
-        <v>1.041345740871147</v>
+        <v>0.07314733217027589</v>
       </c>
     </row>
     <row r="58">
@@ -3576,10 +3576,10 @@
         <v>0.01090017927646798</v>
       </c>
       <c r="M58" t="n">
-        <v>0.0241951959563715</v>
+        <v>0.5744518806230234</v>
       </c>
       <c r="N58" t="n">
-        <v>1.022453357917308</v>
+        <v>0.04306445880937693</v>
       </c>
     </row>
     <row r="59">
@@ -3630,10 +3630,10 @@
         <v>0.008563778726911917</v>
       </c>
       <c r="M59" t="n">
-        <v>0.02506055147093447</v>
+        <v>0.6429151076043956</v>
       </c>
       <c r="N59" t="n">
-        <v>1.038630693352978</v>
+        <v>0.04048537301767816</v>
       </c>
     </row>
     <row r="60">
@@ -3684,10 +3684,10 @@
         <v>0.01672962581950657</v>
       </c>
       <c r="M60" t="n">
-        <v>0.04474508614777217</v>
+        <v>0.6559508518665338</v>
       </c>
       <c r="N60" t="n">
-        <v>1.035307418129013</v>
+        <v>0.07062254661578822</v>
       </c>
     </row>
     <row r="61">
@@ -3738,10 +3738,10 @@
         <v>0.005567315115064913</v>
       </c>
       <c r="M61" t="n">
-        <v>0.04196155469239227</v>
+        <v>0.624483475531688</v>
       </c>
       <c r="N61" t="n">
-        <v>1.034409606350561</v>
+        <v>0.06950613902835369</v>
       </c>
     </row>
     <row r="62">
@@ -3792,10 +3792,10 @@
         <v>0.0107056836999868</v>
       </c>
       <c r="M62" t="n">
-        <v>0.02395656693500777</v>
+        <v>0.577684291467868</v>
       </c>
       <c r="N62" t="n">
-        <v>1.021684864534631</v>
+        <v>0.04236927021421293</v>
       </c>
     </row>
     <row r="63">
@@ -3846,10 +3846,10 @@
         <v>0.007966651671683329</v>
       </c>
       <c r="M63" t="n">
-        <v>0.0248565479887341</v>
+        <v>0.6684184821005454</v>
       </c>
       <c r="N63" t="n">
-        <v>1.038129326317226</v>
+        <v>0.03860502381236487</v>
       </c>
     </row>
     <row r="64">
@@ -3900,10 +3900,10 @@
         <v>0.01834081208076097</v>
       </c>
       <c r="M64" t="n">
-        <v>0.0449213399114869</v>
+        <v>0.6684746760007089</v>
       </c>
       <c r="N64" t="n">
-        <v>1.033006752651791</v>
+        <v>0.06941780912981535</v>
       </c>
     </row>
     <row r="65">
@@ -3954,10 +3954,10 @@
         <v>0.00576964869262816</v>
       </c>
       <c r="M65" t="n">
-        <v>0.04229137955445521</v>
+        <v>0.6385413852111044</v>
       </c>
       <c r="N65" t="n">
-        <v>1.029607306005856</v>
+        <v>0.06819215540107572</v>
       </c>
     </row>
     <row r="66">
@@ -4008,10 +4008,10 @@
         <v>0.008665843262894261</v>
       </c>
       <c r="M66" t="n">
-        <v>0.02423318318175136</v>
+        <v>0.5953839958631545</v>
       </c>
       <c r="N66" t="n">
-        <v>1.027204077433941</v>
+        <v>0.04180902534575347</v>
       </c>
     </row>
     <row r="67">
@@ -4062,10 +4062,10 @@
         <v>0.008642455342039206</v>
       </c>
       <c r="M67" t="n">
-        <v>0.0227176804227838</v>
+        <v>0.6805589086326084</v>
       </c>
       <c r="N67" t="n">
-        <v>1.04135334400671</v>
+        <v>0.03476132951352298</v>
       </c>
     </row>
     <row r="68">
@@ -4116,10 +4116,10 @@
         <v>0.01882272518071008</v>
       </c>
       <c r="M68" t="n">
-        <v>0.04100718952865304</v>
+        <v>0.6947127364122128</v>
       </c>
       <c r="N68" t="n">
-        <v>1.028838851958299</v>
+        <v>0.06072983491648868</v>
       </c>
     </row>
     <row r="69">
@@ -4170,10 +4170,10 @@
         <v>0.005622437317282039</v>
       </c>
       <c r="M69" t="n">
-        <v>0.04238300177405969</v>
+        <v>0.658595497597406</v>
       </c>
       <c r="N69" t="n">
-        <v>1.017048236066221</v>
+        <v>0.06545073167179316</v>
       </c>
     </row>
     <row r="70">
@@ -4224,10 +4224,10 @@
         <v>0.007313845262303325</v>
       </c>
       <c r="M70" t="n">
-        <v>0.02438689336590067</v>
+        <v>0.6111582780281156</v>
       </c>
       <c r="N70" t="n">
-        <v>1.02515329214211</v>
+        <v>0.04090643114551996</v>
       </c>
     </row>
     <row r="71">
@@ -4278,10 +4278,10 @@
         <v>0.005962867759101964</v>
       </c>
       <c r="M71" t="n">
-        <v>0.02111454242546383</v>
+        <v>0.686145116928202</v>
       </c>
       <c r="N71" t="n">
-        <v>1.04054332577815</v>
+        <v>0.03202033455551791</v>
       </c>
     </row>
     <row r="72">
@@ -4332,10 +4332,10 @@
         <v>0.0147517042506812</v>
       </c>
       <c r="M72" t="n">
-        <v>0.03960597768448311</v>
+        <v>0.7060645338951592</v>
       </c>
       <c r="N72" t="n">
-        <v>1.025564474970187</v>
+        <v>0.0575280045374707</v>
       </c>
     </row>
     <row r="73">
@@ -4386,10 +4386,10 @@
         <v>0.005701168764623488</v>
       </c>
       <c r="M73" t="n">
-        <v>0.04152698077250187</v>
+        <v>0.6724674463159386</v>
       </c>
       <c r="N73" t="n">
-        <v>1.021086692399422</v>
+        <v>0.06305531617125558</v>
       </c>
     </row>
     <row r="74">
@@ -4440,10 +4440,10 @@
         <v>0.007154610075165223</v>
       </c>
       <c r="M74" t="n">
-        <v>0.02302589615015578</v>
+        <v>0.6363457737501406</v>
       </c>
       <c r="N74" t="n">
-        <v>1.028619104078975</v>
+        <v>0.03722013667036401</v>
       </c>
     </row>
     <row r="75">
@@ -4494,10 +4494,10 @@
         <v>0.004880208795921642</v>
       </c>
       <c r="M75" t="n">
-        <v>0.02037882504109474</v>
+        <v>0.698217776871347</v>
       </c>
       <c r="N75" t="n">
-        <v>1.037792427760322</v>
+        <v>0.03028996255160867</v>
       </c>
     </row>
     <row r="76">
@@ -4548,10 +4548,10 @@
         <v>0.01475696250557815</v>
       </c>
       <c r="M76" t="n">
-        <v>0.03534464027170819</v>
+        <v>0.7022621127599681</v>
       </c>
       <c r="N76" t="n">
-        <v>1.030815764010355</v>
+        <v>0.05188064641870414</v>
       </c>
     </row>
     <row r="77">
@@ -4602,10 +4602,10 @@
         <v>0.005490871614548416</v>
       </c>
       <c r="M77" t="n">
-        <v>0.03866660724536687</v>
+        <v>0.6606446945903861</v>
       </c>
       <c r="N77" t="n">
-        <v>1.020392855816404</v>
+        <v>0.05972216247993057</v>
       </c>
     </row>
   </sheetData>

--- a/data/summarized fitur aset - KBMI 4.xlsx
+++ b/data/summarized fitur aset - KBMI 4.xlsx
@@ -543,7 +543,7 @@
         <v>0.002152968381480607</v>
       </c>
       <c r="J2" t="n">
-        <v>3.041035192761288e-06</v>
+        <v>0.1644484328203102</v>
       </c>
       <c r="K2" t="n">
         <v>0.01030982340170281</v>
@@ -597,7 +597,7 @@
         <v>0.00142788874342694</v>
       </c>
       <c r="J3" t="n">
-        <v>1.519203062947984e-05</v>
+        <v>0.1247536676290339</v>
       </c>
       <c r="K3" t="n">
         <v>0.0002198516391491816</v>
@@ -651,7 +651,7 @@
         <v>0.0004002192219994195</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0003570887586805681</v>
+        <v>0.1111587671201918</v>
       </c>
       <c r="K4" t="n">
         <v>0.000527329254987367</v>
@@ -705,7 +705,7 @@
         <v>0.0001437675400292877</v>
       </c>
       <c r="J5" t="n">
-        <v>9.84611569726866e-05</v>
+        <v>0.1176079590799003</v>
       </c>
       <c r="K5" t="n">
         <v>0.01512441281699037</v>
@@ -759,7 +759,7 @@
         <v>9.201133468794391e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.00011555659591645</v>
+        <v>0.1872512823839496</v>
       </c>
       <c r="K6" t="n">
         <v>0.1098820814528654</v>
@@ -813,7 +813,7 @@
         <v>0.001481827156031136</v>
       </c>
       <c r="J7" t="n">
-        <v>3.548473540800532e-05</v>
+        <v>0.139331060341151</v>
       </c>
       <c r="K7" t="n">
         <v>0.04589576318289336</v>
@@ -867,7 +867,7 @@
         <v>0.0006827146801328906</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0003296622725965068</v>
+        <v>0.1008664864575047</v>
       </c>
       <c r="K8" t="n">
         <v>0.05596200983367758</v>
@@ -921,7 +921,7 @@
         <v>0.0001966348473467315</v>
       </c>
       <c r="J9" t="n">
-        <v>0.002302644402410447</v>
+        <v>0.2184316888086574</v>
       </c>
       <c r="K9" t="n">
         <v>0.009603750949317584</v>
@@ -975,7 +975,7 @@
         <v>0.001022417400075846</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0001144039520963204</v>
+        <v>0.1838815341150044</v>
       </c>
       <c r="K10" t="n">
         <v>0.1387005912938331</v>
@@ -1029,7 +1029,7 @@
         <v>0.002140459665320387</v>
       </c>
       <c r="J11" t="n">
-        <v>5.495161533800448e-05</v>
+        <v>0.1429996203095563</v>
       </c>
       <c r="K11" t="n">
         <v>0.04469939521487348</v>
@@ -1083,7 +1083,7 @@
         <v>0.001785094854553366</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0003143281632466137</v>
+        <v>0.1105402708039445</v>
       </c>
       <c r="K12" t="n">
         <v>0.01059129547792314</v>
@@ -1137,7 +1137,7 @@
         <v>0.001108929263030272</v>
       </c>
       <c r="J13" t="n">
-        <v>0.001172150495183833</v>
+        <v>0.2057949869772399</v>
       </c>
       <c r="K13" t="n">
         <v>0.03078583244618502</v>
@@ -1191,7 +1191,7 @@
         <v>0.0001888534323677956</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0001253082715570447</v>
+        <v>0.1879260344708674</v>
       </c>
       <c r="K14" t="n">
         <v>0.1671454543858092</v>
@@ -1245,7 +1245,7 @@
         <v>0.001114696161566009</v>
       </c>
       <c r="J15" t="n">
-        <v>3.18364943518697e-05</v>
+        <v>0.163536906997802</v>
       </c>
       <c r="K15" t="n">
         <v>0.02793758330821281</v>
@@ -1299,7 +1299,7 @@
         <v>0.0006637955905848453</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0003069954040020956</v>
+        <v>0.1171658533726254</v>
       </c>
       <c r="K16" t="n">
         <v>0.02381554306055235</v>
@@ -1353,7 +1353,7 @@
         <v>0.0003945302707724037</v>
       </c>
       <c r="J17" t="n">
-        <v>0.001212104734843975</v>
+        <v>0.2164028370431045</v>
       </c>
       <c r="K17" t="n">
         <v>0.01530167066825774</v>
@@ -1407,7 +1407,7 @@
         <v>0.0002377828599528229</v>
       </c>
       <c r="J18" t="n">
-        <v>8.921758050287515e-05</v>
+        <v>0.1876778636824211</v>
       </c>
       <c r="K18" t="n">
         <v>0.1171963698532051</v>
@@ -1461,7 +1461,7 @@
         <v>0.001079855437795084</v>
       </c>
       <c r="J19" t="n">
-        <v>2.999043793377942e-05</v>
+        <v>0.1699496033402223</v>
       </c>
       <c r="K19" t="n">
         <v>0.01235124727829642</v>
@@ -1515,7 +1515,7 @@
         <v>0.0002495093505355219</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0003097054491008251</v>
+        <v>0.125344345302642</v>
       </c>
       <c r="K20" t="n">
         <v>0.007037880758373341</v>
@@ -1569,7 +1569,7 @@
         <v>0.0004391647817716443</v>
       </c>
       <c r="J21" t="n">
-        <v>0.001511432532444023</v>
+        <v>0.2113494446571284</v>
       </c>
       <c r="K21" t="n">
         <v>0.01137849684805179</v>
@@ -1623,7 +1623,7 @@
         <v>0.0008324783177024114</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0001674413045524428</v>
+        <v>0.1916976658740465</v>
       </c>
       <c r="K22" t="n">
         <v>0.1117563918521252</v>
@@ -1677,7 +1677,7 @@
         <v>0.001235298734989432</v>
       </c>
       <c r="J23" t="n">
-        <v>2.681559604915669e-05</v>
+        <v>0.2029915280404975</v>
       </c>
       <c r="K23" t="n">
         <v>0.005545920800043172</v>
@@ -1731,7 +1731,7 @@
         <v>0.0005179801303708352</v>
       </c>
       <c r="J24" t="n">
-        <v>0.000288295790314243</v>
+        <v>0.1230815223355095</v>
       </c>
       <c r="K24" t="n">
         <v>0.02850652602868677</v>
@@ -1785,7 +1785,7 @@
         <v>0.0007057053895885082</v>
       </c>
       <c r="J25" t="n">
-        <v>0.001007984348147997</v>
+        <v>0.2281544597022453</v>
       </c>
       <c r="K25" t="n">
         <v>0.0196164459270966</v>
@@ -1839,7 +1839,7 @@
         <v>0.001103354664961931</v>
       </c>
       <c r="J26" t="n">
-        <v>0.000162770082851472</v>
+        <v>0.1848248956855824</v>
       </c>
       <c r="K26" t="n">
         <v>0.1207216848100681</v>
@@ -1893,7 +1893,7 @@
         <v>0.001234581625278127</v>
       </c>
       <c r="J27" t="n">
-        <v>4.476688473585271e-05</v>
+        <v>0.1955856046568525</v>
       </c>
       <c r="K27" t="n">
         <v>0.01633034415820346</v>
@@ -1947,7 +1947,7 @@
         <v>0.0005250501033175204</v>
       </c>
       <c r="J28" t="n">
-        <v>0.000344427504473789</v>
+        <v>0.1291136965817939</v>
       </c>
       <c r="K28" t="n">
         <v>0.02338579235327528</v>
@@ -2001,7 +2001,7 @@
         <v>0.0004642046590377285</v>
       </c>
       <c r="J29" t="n">
-        <v>0.0009147251031686451</v>
+        <v>0.2235445462952991</v>
       </c>
       <c r="K29" t="n">
         <v>0.03450309283635069</v>
@@ -2055,7 +2055,7 @@
         <v>0.0006161768875860391</v>
       </c>
       <c r="J30" t="n">
-        <v>0.0001543539197971494</v>
+        <v>0.181335961913541</v>
       </c>
       <c r="K30" t="n">
         <v>0.1602437005933967</v>
@@ -2109,7 +2109,7 @@
         <v>0.001043213265568339</v>
       </c>
       <c r="J31" t="n">
-        <v>3.65339596423152e-05</v>
+        <v>0.2073435343367977</v>
       </c>
       <c r="K31" t="n">
         <v>0.002137620642960805</v>
@@ -2163,7 +2163,7 @@
         <v>0.0006054232954529538</v>
       </c>
       <c r="J32" t="n">
-        <v>0.000337129286533113</v>
+        <v>0.1375940432094604</v>
       </c>
       <c r="K32" t="n">
         <v>0.02344281288828923</v>
@@ -2217,7 +2217,7 @@
         <v>0.0004555642689077571</v>
       </c>
       <c r="J33" t="n">
-        <v>0.00107220522361316</v>
+        <v>0.225199637034512</v>
       </c>
       <c r="K33" t="n">
         <v>0.00990671589874278</v>
@@ -2271,7 +2271,7 @@
         <v>0.0001500505017643599</v>
       </c>
       <c r="J34" t="n">
-        <v>0.0001685589764109636</v>
+        <v>0.1855248963820321</v>
       </c>
       <c r="K34" t="n">
         <v>0.07636896630311298</v>
@@ -2325,7 +2325,7 @@
         <v>0.001101446075715182</v>
       </c>
       <c r="J35" t="n">
-        <v>2.735043661512882e-05</v>
+        <v>0.205858937472799</v>
       </c>
       <c r="K35" t="n">
         <v>0.001073869572777991</v>
@@ -2379,7 +2379,7 @@
         <v>0.0006281995649171324</v>
       </c>
       <c r="J36" t="n">
-        <v>0.0003535008448106411</v>
+        <v>0.144628730425321</v>
       </c>
       <c r="K36" t="n">
         <v>0.005528250390249807</v>
@@ -2433,7 +2433,7 @@
         <v>0.000399631603298277</v>
       </c>
       <c r="J37" t="n">
-        <v>0.0009742373800665727</v>
+        <v>0.2124172893143048</v>
       </c>
       <c r="K37" t="n">
         <v>0.00488689606787273</v>
@@ -2487,7 +2487,7 @@
         <v>0.0001497595512472407</v>
       </c>
       <c r="J38" t="n">
-        <v>0.0001399818018258626</v>
+        <v>0.1942098940472354</v>
       </c>
       <c r="K38" t="n">
         <v>0.1316466535350103</v>
@@ -2541,7 +2541,7 @@
         <v>0.001517016800421772</v>
       </c>
       <c r="J39" t="n">
-        <v>1.429244135001508e-05</v>
+        <v>0.1870220073984881</v>
       </c>
       <c r="K39" t="n">
         <v>0.005283543564457215</v>
@@ -2595,7 +2595,7 @@
         <v>0.0007776780227835235</v>
       </c>
       <c r="J40" t="n">
-        <v>0.0004064899760906931</v>
+        <v>0.1461772029090755</v>
       </c>
       <c r="K40" t="n">
         <v>0.001978024973294149</v>
@@ -2649,7 +2649,7 @@
         <v>0.0005666547036586925</v>
       </c>
       <c r="J41" t="n">
-        <v>0.001216704069510063</v>
+        <v>0.2013612114520018</v>
       </c>
       <c r="K41" t="n">
         <v>0.008357338226547873</v>
@@ -2703,7 +2703,7 @@
         <v>7.81678587794987e-05</v>
       </c>
       <c r="J42" t="n">
-        <v>0.0001262219469669672</v>
+        <v>0.1899124478761951</v>
       </c>
       <c r="K42" t="n">
         <v>0.1187570465800469</v>
@@ -2757,7 +2757,7 @@
         <v>0.001433273925325181</v>
       </c>
       <c r="J43" t="n">
-        <v>1.135683364060561e-05</v>
+        <v>0.1783569956948653</v>
       </c>
       <c r="K43" t="n">
         <v>0.004019865064679635</v>
@@ -2811,7 +2811,7 @@
         <v>0.0006869152390269745</v>
       </c>
       <c r="J44" t="n">
-        <v>0.0003228607983280175</v>
+        <v>0.1346956751428122</v>
       </c>
       <c r="K44" t="n">
         <v>0.01142318057789843</v>
@@ -2865,7 +2865,7 @@
         <v>0.000520507008989627</v>
       </c>
       <c r="J45" t="n">
-        <v>0.0009780223928756635</v>
+        <v>0.1929346160837806</v>
       </c>
       <c r="K45" t="n">
         <v>0.02913468486605727</v>
@@ -2919,7 +2919,7 @@
         <v>0.000281208720998448</v>
       </c>
       <c r="J46" t="n">
-        <v>9.219720181348938e-05</v>
+        <v>0.2073406640288415</v>
       </c>
       <c r="K46" t="n">
         <v>0.1003339833606077</v>
@@ -2973,7 +2973,7 @@
         <v>0.001938740751636657</v>
       </c>
       <c r="J47" t="n">
-        <v>1.170706602992187e-05</v>
+        <v>0.186136115018348</v>
       </c>
       <c r="K47" t="n">
         <v>0.0001085912813623963</v>
@@ -3027,7 +3027,7 @@
         <v>0.0009663868550070941</v>
       </c>
       <c r="J48" t="n">
-        <v>0.0003061692833305485</v>
+        <v>0.1398138458565664</v>
       </c>
       <c r="K48" t="n">
         <v>0.00995162668102492</v>
@@ -3081,7 +3081,7 @@
         <v>0.001142966590936983</v>
       </c>
       <c r="J49" t="n">
-        <v>0.001048832773433912</v>
+        <v>0.1960173744915077</v>
       </c>
       <c r="K49" t="n">
         <v>0.02261728629046759</v>
@@ -3135,7 +3135,7 @@
         <v>7.834738564132627e-05</v>
       </c>
       <c r="J50" t="n">
-        <v>9.099608939943467e-05</v>
+        <v>0.2135107283112657</v>
       </c>
       <c r="K50" t="n">
         <v>0.09676324178769634</v>
@@ -3189,7 +3189,7 @@
         <v>0.001260450830698464</v>
       </c>
       <c r="J51" t="n">
-        <v>7.287284122477722e-06</v>
+        <v>0.1717884125302199</v>
       </c>
       <c r="K51" t="n">
         <v>0.00725937505454134</v>
@@ -3243,7 +3243,7 @@
         <v>0.0007202633286479098</v>
       </c>
       <c r="J52" t="n">
-        <v>0.0003220784615706704</v>
+        <v>0.1336227305396449</v>
       </c>
       <c r="K52" t="n">
         <v>0.008585791245612621</v>
@@ -3297,7 +3297,7 @@
         <v>0.0006584474296940396</v>
       </c>
       <c r="J53" t="n">
-        <v>0.001376285995116363</v>
+        <v>0.1778085867761017</v>
       </c>
       <c r="K53" t="n">
         <v>0.01322678164714569</v>
@@ -3351,7 +3351,7 @@
         <v>7.777553347316927e-05</v>
       </c>
       <c r="J54" t="n">
-        <v>8.932741450877359e-05</v>
+        <v>0.2203249378832497</v>
       </c>
       <c r="K54" t="n">
         <v>0.09368933836951662</v>
@@ -3405,7 +3405,7 @@
         <v>0.001779781591707239</v>
       </c>
       <c r="J55" t="n">
-        <v>7.189939544708149e-06</v>
+        <v>0.1643343482987051</v>
       </c>
       <c r="K55" t="n">
         <v>0.00321438709352336</v>
@@ -3459,7 +3459,7 @@
         <v>0.0008361021895316745</v>
       </c>
       <c r="J56" t="n">
-        <v>0.0003233586965631575</v>
+        <v>0.1392520671741181</v>
       </c>
       <c r="K56" t="n">
         <v>0.004543548386411247</v>
@@ -3513,7 +3513,7 @@
         <v>0.0005928946384811503</v>
       </c>
       <c r="J57" t="n">
-        <v>0.001677723495804536</v>
+        <v>0.1880704443242877</v>
       </c>
       <c r="K57" t="n">
         <v>0.01531277816740595</v>
@@ -3567,7 +3567,7 @@
         <v>0.0001586684740422526</v>
       </c>
       <c r="J58" t="n">
-        <v>0.0002595517855674669</v>
+        <v>0.2348439118819193</v>
       </c>
       <c r="K58" t="n">
         <v>0.06622094423142484</v>
@@ -3621,7 +3621,7 @@
         <v>0.001165818486638768</v>
       </c>
       <c r="J59" t="n">
-        <v>6.326196858462391e-06</v>
+        <v>0.1432762636342118</v>
       </c>
       <c r="K59" t="n">
         <v>0.009595627975061864</v>
@@ -3675,7 +3675,7 @@
         <v>0.0009494160144695297</v>
       </c>
       <c r="J60" t="n">
-        <v>0.0002981113097075762</v>
+        <v>0.1351971591329141</v>
       </c>
       <c r="K60" t="n">
         <v>0.009486356388394389</v>
@@ -3729,7 +3729,7 @@
         <v>0.000493433388457687</v>
       </c>
       <c r="J61" t="n">
-        <v>0.001301888926357198</v>
+        <v>0.1848806917932695</v>
       </c>
       <c r="K61" t="n">
         <v>0.01817201910382359</v>
@@ -3783,7 +3783,7 @@
         <v>8.739716856009213e-05</v>
       </c>
       <c r="J62" t="n">
-        <v>0.0002590146304550042</v>
+        <v>0.2363605481947554</v>
       </c>
       <c r="K62" t="n">
         <v>0.04723701111145103</v>
@@ -3837,7 +3837,7 @@
         <v>0.001784198630715182</v>
       </c>
       <c r="J63" t="n">
-        <v>6.702268608649866e-06</v>
+        <v>0.1402516260985411</v>
       </c>
       <c r="K63" t="n">
         <v>0.000327580054112949</v>
@@ -3891,7 +3891,7 @@
         <v>0.001349589821206392</v>
       </c>
       <c r="J64" t="n">
-        <v>0.0002755255167505035</v>
+        <v>0.1423084650453786</v>
       </c>
       <c r="K64" t="n">
         <v>0.009072628594821268</v>
@@ -3945,7 +3945,7 @@
         <v>0.0004035397058766581</v>
       </c>
       <c r="J65" t="n">
-        <v>0.001011234325230556</v>
+        <v>0.2050728994199549</v>
       </c>
       <c r="K65" t="n">
         <v>7.869429835668685e-05</v>
@@ -3999,7 +3999,7 @@
         <v>0.0001202060229946897</v>
       </c>
       <c r="J66" t="n">
-        <v>0.0002684689268625529</v>
+        <v>0.2567295446484266</v>
       </c>
       <c r="K66" t="n">
         <v>0.03613088048708189</v>
@@ -4053,7 +4053,7 @@
         <v>0.002334133279275165</v>
       </c>
       <c r="J67" t="n">
-        <v>6.191113099871456e-06</v>
+        <v>0.128367550665992</v>
       </c>
       <c r="K67" t="n">
         <v>0.002263947985359593</v>
@@ -4107,7 +4107,7 @@
         <v>0.001489420393269885</v>
       </c>
       <c r="J68" t="n">
-        <v>3.560824730313819e-05</v>
+        <v>0.1354450007923447</v>
       </c>
       <c r="K68" t="n">
         <v>0.004580012739095163</v>
@@ -4161,7 +4161,7 @@
         <v>0.0004133543855130349</v>
       </c>
       <c r="J69" t="n">
-        <v>0.0005343850236306456</v>
+        <v>0.2026869557898988</v>
       </c>
       <c r="K69" t="n">
         <v>0.001319331076812697</v>
@@ -4215,7 +4215,7 @@
         <v>0.0002693458336001236</v>
       </c>
       <c r="J70" t="n">
-        <v>0.0002802211526872208</v>
+        <v>0.2854982669844388</v>
       </c>
       <c r="K70" t="n">
         <v>0.001012099822278873</v>
@@ -4269,7 +4269,7 @@
         <v>0.003073270445075793</v>
       </c>
       <c r="J71" t="n">
-        <v>5.800093544576674e-06</v>
+        <v>0.1195428409952728</v>
       </c>
       <c r="K71" t="n">
         <v>0.001206879527615078</v>
@@ -4323,7 +4323,7 @@
         <v>0.001860147654673252</v>
       </c>
       <c r="J72" t="n">
-        <v>3.397285175690322e-05</v>
+        <v>0.1377336398920816</v>
       </c>
       <c r="K72" t="n">
         <v>0.002252379136818217</v>
@@ -4377,7 +4377,7 @@
         <v>0.00273367241151346</v>
       </c>
       <c r="J73" t="n">
-        <v>0.000694469091956496</v>
+        <v>0.1581320431355804</v>
       </c>
       <c r="K73" t="n">
         <v>0.005590316393934529</v>
@@ -4431,7 +4431,7 @@
         <v>0.0001556668897935462</v>
       </c>
       <c r="J74" t="n">
-        <v>0.0002684789697529646</v>
+        <v>0.2712852089064252</v>
       </c>
       <c r="K74" t="n">
         <v>0.0006135466551166029</v>
@@ -4485,7 +4485,7 @@
         <v>0.004123751881620743</v>
       </c>
       <c r="J75" t="n">
-        <v>5.001806493768772e-06</v>
+        <v>0.09283690088184704</v>
       </c>
       <c r="K75" t="n">
         <v>0.00381728176942219</v>
@@ -4539,7 +4539,7 @@
         <v>0.001653391133129313</v>
       </c>
       <c r="J76" t="n">
-        <v>3.307929418409748e-05</v>
+        <v>0.1360212342068167</v>
       </c>
       <c r="K76" t="n">
         <v>0.006714399575460014</v>
@@ -4593,7 +4593,7 @@
         <v>0.0005832997614200835</v>
       </c>
       <c r="J77" t="n">
-        <v>0.0006092251733118512</v>
+        <v>0.1689573600741151</v>
       </c>
       <c r="K77" t="n">
         <v>0.009045819755109635</v>
